--- a/3_meta-analysis/data/sheets_for_analysis/xlsx/pivot_shift_2.xlsx
+++ b/3_meta-analysis/data/sheets_for_analysis/xlsx/pivot_shift_2.xlsx
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>25</v>
@@ -568,11 +568,11 @@
       <c r="Q2" t="n">
         <v>24</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.008</v>
       </c>
     </row>
     <row r="3">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="J3" t="n">
         <v>23.6</v>
@@ -636,10 +636,10 @@
         <v>35.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.194</v>
+        <v>1.212</v>
       </c>
       <c r="S3" t="n">
-        <v>0.42066556509559</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="4">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
         <v>28.5</v>
@@ -703,10 +703,10 @@
         <v>36</v>
       </c>
       <c r="R4" t="n">
-        <v>7.875</v>
+        <v>5.688</v>
       </c>
       <c r="S4" t="n">
-        <v>1.129949429968313</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="5">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>62.5</v>
       </c>
       <c r="G5" t="n">
-        <v>62</v>
+        <v>62.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
         <v>27.9</v>
@@ -769,15 +769,11 @@
       <c r="Q5" t="n">
         <v>29.7</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R5" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.643</v>
       </c>
     </row>
     <row r="6">
@@ -803,16 +799,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
         <v>28.2</v>
@@ -841,10 +837,10 @@
         <v>191.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.404</v>
+        <v>1.408</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4413483586994857</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="7">
@@ -870,16 +866,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G7" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>27</v>
@@ -907,11 +903,11 @@
       <c r="Q7" t="n">
         <v>6.7</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R7" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.011</v>
       </c>
     </row>
     <row r="8">
@@ -937,16 +933,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G8" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>25.8</v>
@@ -974,11 +970,11 @@
       <c r="Q8" t="n">
         <v>36</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R8" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.011</v>
       </c>
     </row>
     <row r="9">
@@ -1004,16 +1000,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>25.2</v>
@@ -1042,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.069</v>
+        <v>1.724</v>
       </c>
       <c r="S9" t="n">
-        <v>1.252124631158585</v>
+        <v>1.065</v>
       </c>
     </row>
     <row r="10">
@@ -1071,16 +1067,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="G10" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1109,12 +1105,10 @@
         <v>60.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.324</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="11">
@@ -1140,16 +1134,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="G11" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J11" t="n">
         <v>29</v>
@@ -1178,10 +1172,10 @@
         <v>24.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0.292</v>
+        <v>0.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7368781568138778</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="12">
@@ -1207,16 +1201,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="G12" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>32.7</v>
@@ -1244,11 +1238,11 @@
       <c r="Q12" t="n">
         <v>24</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R12" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="13">
@@ -1274,16 +1268,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>22.3</v>
@@ -1311,11 +1305,11 @@
       <c r="Q13" t="n">
         <v>81</v>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.012</v>
       </c>
     </row>
     <row r="14">
@@ -1341,16 +1335,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G14" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1378,11 +1372,11 @@
       <c r="Q14" t="n">
         <v>24</v>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.011</v>
       </c>
     </row>
     <row r="15">
@@ -1408,16 +1402,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>29.9</v>
@@ -1445,11 +1439,11 @@
       <c r="Q15" t="n">
         <v>19</v>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R15" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.036</v>
       </c>
     </row>
     <row r="16">
@@ -1475,16 +1469,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>32</v>
@@ -1512,15 +1506,11 @@
       <c r="Q16" t="n">
         <v>24</v>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R16" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.645</v>
       </c>
     </row>
     <row r="17">
@@ -1546,16 +1536,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G17" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>29.8</v>
@@ -1584,12 +1574,10 @@
         <v>73.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.323</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.652</v>
       </c>
     </row>
     <row r="18">
@@ -1615,16 +1603,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="G18" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>27.1</v>
@@ -1652,11 +1640,11 @@
       <c r="Q18" t="n">
         <v>24</v>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R18" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="19">
@@ -1682,16 +1670,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="G19" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1702,10 +1690,10 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.408</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8212372628065205</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="20">
@@ -1731,16 +1719,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G20" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>25.8</v>
@@ -1769,10 +1757,10 @@
         <v>31.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0.302</v>
+        <v>0.388</v>
       </c>
       <c r="S20" t="n">
-        <v>1.182821242603473</v>
+        <v>1.009</v>
       </c>
     </row>
     <row r="21">
@@ -1798,16 +1786,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>25</v>
@@ -1835,11 +1823,11 @@
       <c r="Q21" t="n">
         <v>120</v>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R21" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.009</v>
       </c>
     </row>
     <row r="22">
@@ -1865,16 +1853,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G22" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>27</v>
@@ -1903,10 +1891,10 @@
         <v>228</v>
       </c>
       <c r="R22" t="n">
-        <v>0.27</v>
+        <v>0.347</v>
       </c>
       <c r="S22" t="n">
-        <v>1.180548048024177</v>
+        <v>1.006</v>
       </c>
     </row>
     <row r="23">
@@ -1932,16 +1920,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G23" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>45.5</v>
@@ -1969,11 +1957,11 @@
       <c r="Q23" t="n">
         <v>204</v>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.021</v>
       </c>
     </row>
     <row r="24">
@@ -1999,16 +1987,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="G24" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>30.1</v>
@@ -2036,15 +2024,11 @@
       <c r="Q24" t="n">
         <v>12</v>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R24" t="n">
+        <v>2.829</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.651</v>
       </c>
     </row>
     <row r="25">
@@ -2070,16 +2054,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="G25" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
         <v>30</v>
@@ -2108,10 +2092,10 @@
         <v>34.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0.616</v>
+        <v>0.66</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9299883284793413</v>
+        <v>0.847</v>
       </c>
     </row>
   </sheetData>
